--- a/src/main/resources/2012/02/Kowalski_Jan.xlsx
+++ b/src/main/resources/2012/02/Kowalski_Jan.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">Przygotowanie pierwszej wersji dokumentacji użytkownika</t>
   </si>
   <si>
-    <t xml:space="preserve">Dokumentacja techniczna</t>
+    <t xml:space="preserve">Naprawa auta</t>
   </si>
   <si>
     <t xml:space="preserve">diagramy klas</t>
@@ -47,10 +47,10 @@
     <t xml:space="preserve">Budowa produktu, paczak, instalka</t>
   </si>
   <si>
-    <t xml:space="preserve">Dorabianie ikonek, splash screen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Naprawa błedu znalezionego przez Anię</t>
+    <t xml:space="preserve">Gotowanie obiadu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mycie podłogi</t>
   </si>
   <si>
     <t xml:space="preserve">Przygotowanie przykładowych danych</t>
@@ -62,13 +62,13 @@
     <t xml:space="preserve">Prezentacja</t>
   </si>
   <si>
-    <t xml:space="preserve">Podsumowanie, naprawa błędu</t>
+    <t xml:space="preserve">Jedzenie obiadu</t>
   </si>
   <si>
     <t xml:space="preserve">Wizyta u klienta, dopytanie o dane</t>
   </si>
   <si>
-    <t xml:space="preserve">Przygotoeanie anomimizatora danych i testy</t>
+    <t xml:space="preserve">Obiad</t>
   </si>
   <si>
     <t xml:space="preserve">Wizyta u klienta, przetworzenie i odebranie danych</t>
@@ -91,6 +91,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -113,12 +114,14 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -163,24 +166,28 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -310,146 +317,146 @@
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultColWidth="9.13671875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="60.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="60.85"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="4" t="n">
         <v>40947</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="1" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="4" t="n">
         <v>40947</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="1" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="4" t="n">
         <v>40948</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="1" t="n">
         <v>4.25</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="4" t="n">
         <v>40948</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="5" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="4" t="n">
         <v>40948</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="5" t="n">
         <v>2.5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="4" t="n">
         <v>40952</v>
       </c>
-      <c r="B7" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="0" t="n">
+      <c r="B7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="1" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3"/>
+      <c r="A8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="4" t="n">
         <v>40953</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="0" t="n">
+      <c r="C9" s="1" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="4" t="n">
         <v>40954</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="0" t="n">
+      <c r="C10" s="1" t="n">
         <v>3.5</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="4" t="n">
         <v>40954</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="0" t="n">
+      <c r="C11" s="1" t="n">
         <v>5.5</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="4" t="n">
         <v>40955</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="0" t="n">
+      <c r="C12" s="1" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="4" t="n">
         <v>40955</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="0" t="n">
-        <v>2</v>
+      <c r="C13" s="1" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -471,73 +478,73 @@
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultColWidth="9.13671875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="60.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="60.85"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="4" t="n">
         <v>40940</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="4" t="n">
+      <c r="C2" s="5" t="n">
         <v>7.25</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="4" t="n">
         <v>40941</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="n">
+        <v>40942</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="4" t="n">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="n">
-        <v>40942</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="1" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="4" t="n">
         <v>40946</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="1" t="n">
         <v>5.5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="4" t="n">
         <v>40947</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="1" t="n">
         <v>2</v>
       </c>
     </row>

--- a/src/main/resources/2012/02/Kowalski_Jan.xlsx
+++ b/src/main/resources/2012/02/Kowalski_Jan.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Projekt1" sheetId="1" state="visible" r:id="rId3"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
   <si>
     <t xml:space="preserve">Data</t>
   </si>
@@ -41,6 +41,9 @@
     <t xml:space="preserve">Naprawa auta</t>
   </si>
   <si>
+    <t xml:space="preserve">4.25</t>
+  </si>
+  <si>
     <t xml:space="preserve">diagramy klas</t>
   </si>
   <si>
@@ -50,15 +53,24 @@
     <t xml:space="preserve">Gotowanie obiadu</t>
   </si>
   <si>
+    <t xml:space="preserve">2.5</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mycie podłogi</t>
   </si>
   <si>
     <t xml:space="preserve">Przygotowanie przykładowych danych</t>
   </si>
   <si>
+    <t xml:space="preserve">3.5</t>
+  </si>
+  <si>
     <t xml:space="preserve">Przygotowanie prezentacji</t>
   </si>
   <si>
+    <t xml:space="preserve">5.5</t>
+  </si>
+  <si>
     <t xml:space="preserve">Prezentacja</t>
   </si>
   <si>
@@ -66,6 +78,12 @@
   </si>
   <si>
     <t xml:space="preserve">Wizyta u klienta, dopytanie o dane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5</t>
   </si>
   <si>
     <t xml:space="preserve">Obiad</t>
@@ -81,10 +99,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="yyyy/mm/dd;@"/>
     <numFmt numFmtId="166" formatCode="d/mm/yyyy"/>
+    <numFmt numFmtId="167" formatCode="@"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -166,7 +185,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -187,8 +206,16 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -339,7 +366,7 @@
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="5" t="n">
         <v>3</v>
       </c>
     </row>
@@ -350,7 +377,7 @@
       <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="5" t="n">
         <v>4</v>
       </c>
     </row>
@@ -361,11 +388,11 @@
       <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="1" t="n">
-        <v>4.25</v>
+      <c r="C4" s="5" t="s">
+        <v>6</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -373,9 +400,9 @@
         <v>40948</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C5" s="6" t="n">
         <v>2</v>
       </c>
     </row>
@@ -384,10 +411,10 @@
         <v>40948</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>2.5</v>
+        <v>9</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -397,21 +424,22 @@
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="5" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4"/>
+      <c r="C8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="n">
         <v>40953</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="C9" s="5" t="n">
         <v>7</v>
       </c>
     </row>
@@ -420,10 +448,10 @@
         <v>40954</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="1" t="n">
-        <v>3.5</v>
+        <v>12</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -431,10 +459,10 @@
         <v>40954</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="1" t="n">
-        <v>5.5</v>
+        <v>14</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -442,9 +470,9 @@
         <v>40955</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="C12" s="5" t="n">
         <v>3</v>
       </c>
     </row>
@@ -453,9 +481,9 @@
         <v>40955</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="C13" s="5" t="n">
         <v>7</v>
       </c>
     </row>
@@ -498,10 +526,10 @@
         <v>40940</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="5" t="n">
-        <v>7.25</v>
+        <v>18</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -509,10 +537,10 @@
         <v>40941</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="5" t="n">
-        <v>6.5</v>
+        <v>9</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -520,9 +548,9 @@
         <v>40942</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="C4" s="5" t="n">
         <v>4</v>
       </c>
     </row>
@@ -531,10 +559,10 @@
         <v>40946</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>5.5</v>
+        <v>22</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -542,9 +570,9 @@
         <v>40947</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="C6" s="5" t="n">
         <v>2</v>
       </c>
     </row>
